--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_04_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_04_19_Cau.xlsx
@@ -723,7 +723,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Consistency hỏi các phần liên quan có đồng ý theo invariant không.</t>
+          <t>Các phép kiểm tra tính nhất quán (consistency checks) trong bộ dữ liệu orders gồm: (a) Tính nhất quán trong bản ghi: `order.total = sum(line.amount)` cùng đơn vị tiền tệ; (b) Tính nhất quán tham chiếu: mọi `customer_id` đều tham chiếu tới một khách hàng tồn tại trong bảng customers; (c) Tính nhất quán giữa các biểu diễn: cùng một order_id phải có cùng trạng thái trên các view tại cùng một thời điểm. Kiểm tra email chứa @ và order.total nằm trong dải là các kiểm tra hợp lệ định dạng/miền giá trị (validity), không phải consistency.</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
@@ -752,7 +756,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Clock dừng ở publish boundary, không ở job start.</t>
+          <t>Độ trễ dữ liệu (freshness lag) được tính từ thời điểm phát sinh sự kiện nguồn (09:00) đến ranh giới xuất bản phục vụ người dùng (09:18): 09:18 - 09:00 = 18 phút. Độ trễ 18 phút đã vượt quá mức SLA tối đa 15 phút là 3 phút.</t>
         </is>
       </c>
     </row>
@@ -950,7 +954,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một operator phải biết check gì và làm gì khi fail.</t>
+          <t>Một hợp đồng dữ liệu (data contract) có tính thực thi cao cho validator và operator cần: (a) Định nghĩa schema chuẩn hóa, các trường bắt buộc, miền giá trị và khóa định danh; (b) Xác định rõ người sở hữu (owner) và nguồn sự thật có thẩm quyền; (c) Quy định mức độ nghiêm trọng và hậu quả xử lý cho từng loại vi phạm; (d) Khi độ mới dữ liệu chưa rõ, chỉ định rõ người ra quyết định thay vì tự ý điền giá trị ngầm định.</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1122,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người review cần tái tạo được lý do pass/fail và biết bản ghi nào cần xử lý.</t>
+          <t>Kết quả kiểm tra kỳ vọng dữ liệu (data expectation result) cần lưu trữ đầy đủ để phục vụ kiểm toán và xử lý lỗi: (a) Tên điều khoản/chiều chất lượng và phạm vi kiểm tra của lần chạy; (b) Giá trị quan sát được kèm mẫu số tính toán; (c) Ngưỡng chấp nhận và mức độ nghiêm trọng của lỗi; (d) Bằng chứng cụ thể về các dòng dữ liệu bị lỗi hoặc lát cắt dữ liệu vi phạm. Chỉ trả về giá trị boolean false là không đủ thông tin chẩn đoán.</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1173,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Liệt kê cả điều suite không quan sát.</t>
+          <t>Khi bộ kiểm tra đạt các tiêu chí not-null, type và range trên phân vùng của ngày hôm nay, các kết luận hợp lý là: (a) Toàn bộ các quy tắc đã triển khai đều đạt yêu cầu trên phạm vi phân vùng hôm nay; (c) Các phân vùng của những ngày khác vẫn chưa được kiểm tra; (d) Các quy tắc nghiệp vụ sâu hơn hoặc tính thẩm quyền của nguồn có thể chưa được kiểm tra trong bộ test này. Không thể suy diễn dữ liệu tương lai chắc chắn đúng hay độ chính xác bên ngoài đã được chứng minh.</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1222,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1232,7 +1240,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là toàn bộ bản ghi mà rule đã chặn.</t>
+          <t>Độ chính xác (Precision) của quy tắc chặn lỗi: Tỷ lệ giữa số bản ghi thực sự bị lỗi (True Positives = 30) trên tổng số bản ghi mà quy tắc đã chặn (Total Predicted Positives = 40): Precision = 30 / 40 = 0,75 = 75%.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_04_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_04_19_Cau.xlsx
@@ -669,10 +669,20 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Có hai invariant độc lập trong scenario.
-Phân tích theo nguyên lý thiết kế: Có hai invariant độc lập trong scenario.</t>
+- [1.5 điểm] Chỉ ra chính xác 2 điểm không nhất quán: chênh lệch số học giữa tổng order (120) và tổng dòng (110), cùng xung đột trạng thái giữa CRM (paid) và Sổ cái (pending).
+- [1.5 điểm] Xác định đúng nguồn giải quyết trạng thái thanh toán là Sổ cái (Ledger - thẩm quyền tối cao), đưa trạng thái về 'pending'.
+- [1.0 điểm] Đưa ra phương án đối soát và điều chỉnh trường số tiền dựa trên dữ liệu dòng hàng/hóa đơn gốc.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Các điểm không nhất quán (Inconsistencies):
+   - Điểm không nhất quán 1 (Toán học nội bộ - Internal Line Sum Invariant): Tổng các dòng hàng là 50 + 60 = 110 VND, trong khi trường `Order.total` lại ghi nhận 120 VND (chênh lệch 10 VND giữa tổng đơn hàng và tổng chi tiết các mục hàng).
+   - Điểm không nhất quán 2 (Trạng thái đa hệ thống - Cross-System State Invariant): Hệ thống CRM ghi nhận trạng thái đơn hàng là `paid` (đã thanh toán), nhưng Hệ thống Sổ cái (General Ledger) lại ghi nhận trạng thái là `pending` (đang chờ xử lý).
+2. Nguồn dùng để giải quyết từng điểm (Authoritative Resolution Source):
+   - Đối với trạng thái thanh toán: Theo bối cảnh đề bài, 'sổ cái là nguồn có thẩm quyền cho thanh toán' (General Ledger is the Authoritative Source of Truth). Do đó, trạng thái chuẩn xác phải là `pending`. Hệ thống CRM phải được đồng bộ lại theo sổ cái.
+   - Đối với giá trị tiền đơn hàng: Cần kiểm tra bản ghi gốc của giao dịch hóa đơn/dòng hàng trên cơ sở dữ liệu bán hàng (Order Management System - OMS); nếu không có phí phụ thu/thuế (10 VND), thì tổng chi tiết các dòng (110 VND) hoặc hóa đơn kế toán là căn cứ để điều chỉnh `Order.total`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong thiết kế kiểm thử tính nhất quán dữ liệu (Data Consistency Check), kỹ sư cần phân định rõ hai loại bất biến (invariants): Bất biến nội bộ (Intra-record arithmetic invariant) và Bất biến liên hệ thống (Inter-system state invariant). Khi xảy ra xung đột giữa các hệ thống phân tán, việc phân xử bắt buộc phải căn cứ vào 'Nguồn có thẩm quyền được chỉ định' (Designated System of Record / Authoritative Source) thay vì dùng đa số biểu quyết hay phỏng đoán ngẫu nhiên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Kleppmann, Designing Data-Intensive Applications - Consistency Guarantees &amp; Systems of Record; Enterprise Integration Patterns - Canonical Data Model</t>
         </is>
       </c>
     </row>
@@ -787,10 +797,23 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Người dùng dữ liệu chưa nhìn thấy bản ghi tại thời điểm làm sạch xong.
-Phân tích theo nguyên lý thiết kế: Người dùng dữ liệu chưa nhìn thấy bản ghi tại thời điểm làm sạch xong.</t>
+- [1.5 điểm] Tính toán chính xác thời gian trễ thực tế là 22 phút (10:22 - 10:00), chỉ ra sự khác biệt bản chất so với thời gian chạy job 3 phút.
+- [1.5 điểm] Phân loại chính xác kết quả là Vi phạm SLA (SLA Breach) vì 22 phút vượt xa ngưỡng cam kết 10 phút.
+- [1.0 điểm] Phân tích được nguyên nhân chậm trễ nằm ở khoảng thời gian sau khi làm sạch đến khi xuất bản (18 phút delay).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính đúng thời gian trễ (Data Freshness Latency):
+   - Thời điểm dữ liệu có hiệu lực tại nguồn: 10:00.
+   - Thời điểm dữ liệu thực sự được xuất bản tới người dùng/agent (Publish Time): 10:22.
+   - Thời gian trễ thực tế đối với người dùng (End-to-End Freshness Latency) = 10:22 - 10:00 = 22 phút.
+   - Lưu ý phân biệt: Thời gian chạy của job (Job Runtime) từ 10:01 đến 10:04 chỉ là 3 phút. Tuy nhiên, dữ liệu nằm chờ từ 10:04 đến 10:22 mới được publish (mất thêm 18 phút ở bước staging/indexing/approval). Do đó, chỉ số 3 phút trên dashboard chỉ là 'Execution Time', hoàn toàn không phải 'Freshness Latency'.
+2. Phân loại kết quả đối với SLA:
+   - Ngưỡng cam kết (SLA): Tối đa 10 phút.
+   - Thực tế: 22 phút &gt; 10 phút.
+   - Kết luận: VI PHẠM SLA NGHIÊM TRỌNG (SLA Breach / Violated), vượt ngưỡng 12 phút (gấp hơn 2.2 lần giới hạn cho phép).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sai lầm phổ biến nhất trong việc giám sát độ tươi của dữ liệu (Data Freshness Monitoring) là dùng thời gian thực thi của tác vụ (Job Execution Duration) để thay thế cho độ trễ dữ liệu từ góc nhìn người dùng (End-to-End Freshness). Người dùng dữ liệu hoặc AI Agent chỉ quan tâm: 'Dữ liệu tôi đang đọc cách thời điểm phát sinh thực tế tại thế giới thực bao lâu?'. Đồng hồ độ tươi phải bắt đầu chạy từ khi nguồn có hiệu lực và chỉ dừng lại khi dữ liệu đã xuất bản sẵn sàng để truy vấn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Service Level Objectives (SLOs) &amp; Latency Measurement: https://sre.google/sre-book/service-level-objectives/ và Monte Carlo Data Observability - Freshness Metrics: https://www.montecarlodata.com/</t>
         </is>
       </c>
     </row>
@@ -866,10 +889,20 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng so hai value mà bỏ ngày chúng có hiệu lực.
-Phân tích theo nguyên lý thiết kế: Đừng so hai value mà bỏ ngày chúng có hiệu lực.</t>
+- [1.5 điểm] Phân loại chính xác giá trị 3 triệu vào ngày 15/6 là KHÔNG CHÍNH XÁC (Inaccurate).
+- [1.5 điểm] Lập luận chặt chẽ dựa trên mốc ngày hiệu lực 01/06 của trang policy thẩm quyền tối cao và xác định nguyên nhân do cache PDF bị cũ (stale).
+- [1.0 điểm] Thiết lập cấu trúc bản ghi lưu vết xung đột (conflict record) đầy đủ thông tin phục vụ kiểm toán và khắc phục.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại tính chính xác (Classification):
+   - Trường hợp ngày 15/6 mang giá trị 3 triệu là: KHÔNG CHÍNH XÁC (Inaccurate / Outdated Data).
+   - Căn cứ: Trang policy có thẩm quyền tối cao (Authoritative Policy Page) quy định hạn mức 5 triệu có hiệu lực từ ngày 01/06. Vì ngày phát sinh sự việc là ngày 15/06 (nằm sau mốc ngày 01/06), chính sách mới 5 triệu đã có hiệu lực bắt buộc thi hành. Giá trị 3 triệu là giá trị của chính sách cũ đã bị thay thế (superseded policy) tồn đọng trong file PDF lưu đệm (cached PDF).
+2. Giữ lại xung đột phục vụ kiểm toán (Conflict Record Architecture):
+   - Ghi nhận bản ghi xung đột (Data Conflict Log) lưu trữ: `case_date='2026-06-15'`, `evaluated_value=3000000`, `authoritative_value=5000000`, `authoritative_source='Official Policy Page'`, `conflicting_source='Cached PDF'`, `discrepancy_reason='Stale cache used post-effective date'`.
+   - Xử lý: Xóa cache PDF cũ, tái lập chỉ mục tìm kiếm với chính sách mới và đưa trường hợp 15/6 vào diện xử lý lại để áp dụng đúng hạn mức 5 triệu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong đánh giá chất lượng dữ liệu về khía cạnh Tính chính xác (Accuracy), việc so sánh hai giá trị không thể tách rời khỏi trục thời gian hiệu lực (Effective Date Range) và thứ bậc nguồn thẩm quyền (Source of Truth Hierarchy). Một giá trị từng đúng trong quá khứ sẽ trở thành sai lệch nếu được áp dụng cho một sự kiện xảy ra sau ngày chính sách mới có hiệu lực. Hệ thống phải chủ động phát hiện sự không đồng bộ giữa bộ đệm (cache) và nguồn gốc để ngăn ngừa sai phạm nghiệp vụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+DAMA-DMBOK: Data Quality Dimensions - Accuracy and Temporal Consistency; ISO 8000-61: Data Quality Management Processes</t>
         </is>
       </c>
     </row>
@@ -900,10 +933,41 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Điều chưa được business xác nhận phải trở thành một field quyết định, không thành con số giả.
-Phân tích theo nguyên lý thiết kế: Điều chưa được business xác nhận phải trở thành một field quyết định, không thành con số giả.</t>
+- [1.5 điểm] Xây dựng Data Contract có cấu trúc đầy đủ, rõ ràng (schema fields, SLAs, SLA status).
+- [1.5 điểm] Tuyệt đối không tự ý bịa ra con số ngưỡng giả; mô hình hóa trạng thái chưa xác nhận thành trường quản trị rõ ràng (UNCONFIRMED / TBD).
+- [1.0 điểm] Thiết lập cơ chế vận hành an toàn: chế độ cảnh báo mềm (warn-only), thu thập baseline và chỉ định escalation owner cùng deadline cụ thể.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Viết Data Contract vận hành được mà không tự chế tạo ngưỡng giả:
+```yaml
+dataset: tickets
+consumer: sla_assistant_agent
+contract_version: 1.0.0
+schema:
+  - field: ticket_id
+    type: string
+    required: true
+  - field: status
+    type: string
+    enum: [open, pending, resolved, closed]
+  - field: updated_at
+    type: timestamp_iso
+    required: true
+service_level_agreements:
+  freshness:
+    metric: current_time - MAX(updated_at)
+    status: UNCONFIRMED_BY_BUSINESS
+    target_threshold: TBD_PENDING_BUSINESS_APPROVAL
+    operational_fallback:
+      action: log_metric_and_warn_only
+      hard_gate_blocking: false
+      escalation_owner: business_ops_lead@company.com
+      decision_gate_deadline: 2026-05-01
+```
+Giải thích cơ chế vận hành: Hợp đồng ghi rõ trường `freshness.status = UNCONFIRMED_BY_BUSINESS`. Trong giai đoạn này, pipeline vẫn đo lường và ghi nhận chỉ số trễ liên tục (telemetry) nhưng không áp dụng hard-block làm sập hệ thống. Việc thiếu ngưỡng được chuyển hóa thành một hạng mục quyết định có người phụ trách (escalation owner) và thời hạn phê duyệt rõ ràng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một sai lầm nghiêm trọng trong Data Engineering là khi nghiệp vụ chưa đưa ra chỉ số, kỹ sư tự tiện gán một con số tưởng tượng (ví dụ tự điền 15 phút). Điều này dẫn đến false alerts hoặc hiểu lầm tai hại về cam kết chất lượng. Thiết kế Data Contract chuẩn mực cho phép ghi nhận các trường ở trạng thái 'Unconfirmed / TBD' nhưng vẫn vận hành được nhờ cơ chế fallback mềm (warn-only, thu thập baseline dữ liệu thực tế) và gán trách nhiệm giải trình rõ ràng cho đại diện nghiệp vụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Data Contracts: Building Production-Ready Data Platforms (Chad Sanderson) và Open Data Contract Standard (ODCS): https://bitol.io/odcs/</t>
         </is>
       </c>
     </row>
@@ -1034,10 +1098,27 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Thiết kế giai đoạn mà old/new consumer cùng chạy.
-Phân tích theo nguyên lý thiết kế: Thiết kế giai đoạn mà old/new consumer cùng chạy.</t>
+- [1.0 điểm] Thiết kế giai đoạn tương thích ngược (Expand phase / dual-field / view aliasing) cho phép các consumer deploy lệch lịch.
+- [1.0 điểm] Xây dựng kế hoạch backfill an toàn cho 2 năm lịch sử và kiểm tra tính toàn vẹn.
+- [1.0 điểm] Thiết lập cơ chế giám sát lưu lượng sử dụng trường cũ trước khi tiến hành deprecation (Contract phase).
+- [1.0 điểm] Xây dựng phương án rollback chi tiết, đảm bảo không làm gián đoạn hệ thống.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Kế hoạch nâng cấp Schema Evolution (đổi `dept` -&gt; `department`):
+1. Versioning &amp; Transition Phase (Giai đoạn chuyển tiếp tương thích ngược):
+   - Ban hành Schema v2 hỗ trợ đồng thời cả hai trường (Dual-Write / Computed Aliasing). Trong bảng hoặc stream, cột `department` mới được bổ sung, đồng thời trường `dept` cũ vẫn được duy trì dưới dạng view alias hoặc được pipeline tự động sao chép (`department = COALESCE(new.department, old.dept)`).
+   - Cho phép 3 consumer triển khai nâng cấp theo lịch trình độc lập mà không bị gián đoạn hoạt động.
+2. Migration &amp; Backfill (Xử lý 2 năm lịch sử):
+   - Chạy job batch backfill ngoài giờ cao điểm: `UPDATE table SET department = dept WHERE department IS NULL;` cho toàn bộ phân vùng 2 năm lịch sử.
+   - Kiểm tra tính đầy đủ: Xác nhận 100% dòng trong lịch sử có `department IS NOT NULL`.
+3. Monitoring (Giám sát chuyển dịch):
+   - Theo dõi log truy vấn hoặc Kafka metrics để đo lường tỷ lệ các consumer còn gọi trường cũ `dept`.
+   - Đặt mốc thời gian Deprecation (ví dụ sau 30 ngày) khi mọi consumer đã chuyển sang đọc `department`.
+4. Rollback Plan (Phương án quay lui):
+   - Nếu một consumer gặp sự cố sau release, consumer đó rollback về code cũ và vẫn đọc bình thường từ trường `dept` vì trường này chưa hề bị xóa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Đổi tên cột (Column Rename) trong hệ thống phân tán là một 'Breaking Change' nếu thực hiện trực tiếp. Khi các ứng dụng tiêu thụ (consumers) có lịch release độc lập, giải pháp chuẩn mực là áp dụng mẫu hình 'Expand and Contract' (Mở rộng và Co hẹp): (1) Expand: Thêm trường mới, hỗ trợ cả hai; (2) Migrate &amp; Backfill: Cập nhật dữ liệu lịch sử và chuyển đổi dần các consumer; (3) Contract: Chỉ xóa trường cũ sau khi kiểm chứng không còn ai sử dụng. Cách tiếp cận này đảm bảo Zero Downtime và cho phép rollback tức thời.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Fowler, Evolutionary Database Design - Parallel Change / Expand and Contract: https://martinfowler.com/bliki/ParallelChange.html và Confluent Schema Registry Compatibility Rules: https://docs.confluent.io/platform/current/schema-registry/avro.html</t>
         </is>
       </c>
     </row>
@@ -1068,10 +1149,23 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính numerator trước rồi gắn consequence từ severity.
-Phân tích theo nguyên lý thiết kế: Tính numerator trước rồi gắn consequence từ severity.</t>
+- [1.5 điểm] Tính toán chính xác toàn bộ số liệu: tử số là 975, tỷ lệ thực tế đạt 97.5% so với ngưỡng hợp đồng 99.0%.
+- [1.5 điểm] Kết luận chính xác trạng thái kiểm thử là FAILED do vi phạm tiêu chuẩn cam kết.
+- [1.0 điểm] Thực thi đúng hệ quả của Hard Gate: chặn xuất bản dữ liệu run R7, cách ly dữ liệu lỗi và gửi cảnh báo khẩn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Evidence từ dữ liệu thực tế:
+   - Tổng số bản ghi của lần chạy R7 (Scope Run): N = 1.000 dòng.
+   - Số bản ghi bị thiếu `source_id`: 25 dòng.
+   - Số bản ghi có `source_id` hợp lệ (Numerator): 1.000 - 25 = 975 dòng.
+   - Tỷ lệ thực tế đạt được: Observed Value = 975 / 1.000 = 0.975 (97.5%).
+   - Ngưỡng kỳ vọng của Hợp đồng dữ liệu (Clause Threshold): Expected Value &gt;= 0.990 (99.0%).
+2. Kết quả Expectation và Quyết định hệ quả (Consequence Gate):
+   - Trạng thái kiểm thử: FAILED (Vi phạm ngưỡng chất lượng: 97.5% &lt; 99.0%, thiếu hụt 1.5% tương đương 15 dòng dưới chuẩn).
+   - Quyết định theo Severity Hard Gate: LẬP TỨC CHẶN PIPELINE (Hard Gate Block / Abort Pipeline). Toàn bộ dữ liệu của Run R7 KHÔNG ĐƯỢC PHÉP xuất bản (no publish) sang bảng serving hoặc vector index của RAG Agent. Đẩy toàn bộ batch hoặc 25 dòng lỗi vào Quarantine, phát tín hiệu P1 Alert cho Data Engineering On-call để xử lý.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một 'Executable Data Expectation' không chỉ dừng lại ở việc tính toán thống kê mà phải gắn liền với một hành động chế tài cụ thể (Automated Enforcement Consequence). Với mức độ nghiêm trọng 'Hard Gate', bất kỳ sự vi phạm ngưỡng nào dù chỉ 1.5% cũng đồng nghĩa với việc toàn bộ lô dữ liệu không đạt tiêu chuẩn chất lượng. Việc tự động chặn xuất bản giúp bảo vệ các mô hình hạ tầng downstream (Agent, Analytics) khỏi việc bị nhiễm độc dữ liệu rác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Great Expectations Documentation - Evaluation Engine &amp; Actions: https://docs.greatexpectations.io/ và Great Expectations Hard vs Soft Gates Design Patterns</t>
         </is>
       </c>
     </row>
@@ -1204,10 +1298,19 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi claim thiếu cần một phép đo khác loại, không thêm nhiều null checks.
-Phân tích theo nguyên lý thiết kế: Mỗi claim thiếu cần một phép đo khác loại, không thêm nhiều null checks.</t>
+- [1.5 điểm] Đưa ra kết luận khách quan, chuẩn xác: ghi nhận tính toàn vẹn cú pháp nhưng nêu rõ giới hạn chưa chứng minh được độ chính xác và độ tươi.
+- [1.5 điểm] Đề xuất Evidence 1 phù hợp: đối soát đối chiếu chéo với Source of Truth (Reconciliation check) để đo lường tính chính xác ngữ nghĩa.
+- [1.0 điểm] Đề xuất Evidence 2 phù hợp: đo lường độ tươi của dữ liệu (Freshness metric / Watermark latency clock).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Viết kết luận hợp lệ về hiện trạng dữ liệu:
+   - Kết luận hợp lệ: 'Bộ kiểm thử xác nhận tập dữ liệu 10.000 dòng thỏa mãn hoàn hảo tính toàn vẹn kỹ thuật cục bộ (Syntactic &amp; Structural Integrity): các trường không bị rỗng, đúng kiểu dữ liệu khai báo và đạt tính duy nhất của khóa. TUY NHIÊN, bộ kiểm thử này CHƯA THỂ CHỨNG MINH tính chính xác thực tế (Real-world Semantic Accuracy) và độ tươi của dữ liệu (Data Freshness), do hoàn toàn thiếu đối chiếu với nguồn chân lý và thiếu đồng hồ đo độ trễ.'
+2. Hai Evidence bổ sung để thu hẹp khoảng trống chất lượng:
+   - Evidence 1 (Source of Truth Reconciliation Check): Thực hiện đối chiếu mẫu hoặc đối chiếu tổng kiểm (Reconciliation Reconciliation / Hash Diff) giữa dataset hiện tại và cơ sở dữ liệu nguồn gốc (Authoritative DB/CRM), đo lường tỷ lệ sai khác giá trị giữa các trường kinh doanh cốt lõi.
+   - Evidence 2 (Data Freshness Latency Metric): Thiết lập phép đo thời gian thực tế `NOW() - MAX(source_event_timestamp)` để chứng minh dữ liệu được cập nhật trong khung thời gian cho phép, phát hiện dữ liệu bị ứ đọng do pipeline bị kẹt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc 'Giới hạn bao phủ của bộ kiểm thử' (Quality Suite Coverage Limits) cảnh báo rằng việc vượt qua 100% các phép kiểm tra cấu trúc cơ bản (Null, Type, Uniqueness) chỉ là điều kiện cần chứ chưa phải điều kiện đủ. Dữ liệu có thể hoàn toàn 'sạch' về mặt cú pháp nhưng lại hoàn toàn 'sai' về mặt ngữ nghĩa (ví dụ: số dư tài khoản đúng format số nguyên nhưng sai số tiền thực tế) hoặc 'cũ rích' do đọc từ snapshot cũ. Cần bổ sung các phép đo khác chiều (Freshness, Ground-truth reconciliation) để đảm bảo chất lượng toàn diện.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Research - 'Data Cascades in High-Stakes AI' (Sambasivan et al., CHI 2021) và Monte Carlo - The 5 Pillars of Data Observability</t>
         </is>
       </c>
     </row>
@@ -1271,10 +1374,25 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: False positives có chung field nào?
-Phân tích theo nguyên lý thiết kế: False positives có chung field nào?</t>
+- [1.5 điểm] Tính toán chính xác độ chuẩn xác Precision = 40 / 100 = 40.0%.
+- [1.5 điểm] Nhận diện đúng đặc điểm chung của false positives và viết lại rule chính xác (kết hợp điều kiện loại trừ account_type='dependent').
+- [1.0 điểm] Nêu rõ hệ quả xử lý cho 2 nhóm: giải phóng 60 tài khoản người phụ thuộc và giữ chặn 40 lỗi thật.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Precision của Rule hiện tại:
+   - Tổng số dòng bị chặn bởi rule (Total Blocked / Predicted Positive): 100 dòng.
+   - Số dòng thực sự bị lỗi (True Positives): 40 dòng.
+   - Số dòng hợp lệ nhưng bị chặn nhầm (False Positives - tài khoản người phụ thuộc): 60 dòng.
+   - Precision = True Positives / (True Positives + False Positives) = 40 / 100 = 0.40 (40.0%).
+2. Hiệu chỉnh Rule (Rule Adjustment):
+   - Phân tích: Điểm chung của các ca bị chặn nhầm là chúng có trường phân loại tài khoản là người phụ thuộc (account_type = 'dependent').
+   - Rule mới chuẩn hóa: `IF (age &lt; 18 AND account_type != 'dependent') THEN BLOCK;`
+3. Lựa chọn hệ quả (Consequence):
+   - Đối với 60 dòng người phụ thuộc: Mở khóa giải phóng khỏi quarantine, đưa vào canonical phục vụ agent bình thường.
+   - Đối với 40 dòng lỗi thực sự: Tiếp tục duy trì trạng thái block, chuyển vào DLQ kèm thông báo lỗi cụ thể để bộ phận CSKH liên hệ cập nhật.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một luật kiểm định dữ liệu có Precision thấp (chỉ 40%) sẽ gây ra tỷ lệ báo động giả (False Positive) cao, trực tiếp làm tắc nghẽn luồng vận hành kinh doanh (chặn oan 60 khách hàng hợp lệ). Khi điều tra các ca false positive, kỹ sư dữ liệu phải tìm ra thuộc tính phân nhóm chung (ở đây là account_type='dependent') để tinh chỉnh điều kiện của luật, nâng Precision lên 100% trong khi vẫn giữ vững khả năng ngăn chặn các lỗi thực sự.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Eliminating Alert Fatigue &amp; Tuning Alert Rules: https://sre.google/sre-book/monitoring-distributed-systems/ và Machine Learning Evaluation Metrics (Precision/Recall in Anomaly Detection)</t>
         </is>
       </c>
     </row>
@@ -1350,10 +1468,21 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Dùng watermark/effective time mà consumer thực sự thấy.
-Phân tích theo nguyên lý thiết kế: Dùng watermark/effective time mà consumer thực sự thấy.</t>
+- [1.5 điểm] Tính toán đầy đủ và chính xác các khoảng thời gian: Source freshness 30 phút, Pipeline execution delay 24 phút, và Consumer freshness lag thực tế là 90 phút (10:30 - 09:00).
+- [1.5 điểm] Diễn giải chính xác ý nghĩa các tín hiệu: scheduler bị gián đoạn và watermark bị treo không tiến lên.
+- [1.0 điểm] Chỉ ra đúng các yếu tố chưa xác định cần điều tra thêm (nguyên nhân kẹt watermark và tình trạng scheduler).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán và diễn giải các chỉ số (Signals) tại thời điểm hiện tại (10:30):
+   - Source Freshness (Độ tươi đầu nguồn): 10:30 - 10:00 = 30 phút. Nguồn đã không có dữ liệu mới trong 30 phút qua.
+   - Schedule Execution Lag: Chu kỳ chạy là 5 phút. Lần chạy thành công gần nhất là 10:05 (xuất bản 10:06). Từ 10:06 đến 10:30 là 24 phút, tương đương đã bỏ lỡ hoặc thất bại gần 5 chu kỳ chạy (chỉ số cảnh báo pipeline bị treo/stalled).
+   - Consumer Freshness Lag (Độ tươi thực tế người dùng nhìn thấy): Dữ liệu mà người dùng thực sự truy vấn được chỉ cập nhật đến mốc `watermark = 09:00`. Do đó: Consumer Latency = 10:30 - 09:00 = 1 giờ 30 phút (90 phút). Mặc dù có dữ liệu nguồn lúc 10:00 và job chạy lúc 10:05, watermark không tiến lên chứng tỏ job chạy nhưng không consume dữ liệu mới.
+2. Nêu điều chưa xác định (Unconfirmed / Unknowns):
+   - Chưa xác định được nguyên nhân vì sao Watermark bị kẹt ở 09:00 (do upstream ngừng sinh transaction, do lỗi phân quyền kết nối, hay do worker gặp poison pill khiến offset commit bị block);
+   - Chưa xác định được trạng thái của các lần chạy từ 10:06 đến 10:30 (job bị crash silently hay scheduler cron bị chết).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quan sát độ tươi của dữ liệu (Data Freshness Observability) đòi hỏi phải phân tích đa chiều: (1) Trạng thái đầu nguồn (Source timestamp); (2) Trạng thái lịch trình (Scheduler execution); (3) Mốc tiến trình thực tế được commit (Consumer Watermark). Sự chênh lệch giữa thời điểm chạy (10:05) và Watermark (09:00) là tín hiệu điển hình của việc pipeline chạy 'rỗng' (empty run) hoặc lỗi commit, khiến người dùng phải tiêu thụ dữ liệu cũ hơn 1.5 giờ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Tyler Akidau, Streaming Systems - Watermarks and Processing Time vs Event Time; Datadog - Monitoring Data Pipeline Freshness</t>
         </is>
       </c>
     </row>
